--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb77d573f54374cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R688b2e2e9fb945fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -447,18 +447,18 @@
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>结果核对</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>物理行去向、压制原因、URL字段、策略指纹、源码坐标、严重级别、最长前缀与报告排序</x:v>
+        <x:v>物理行去向、压制原因、URL字段、策略指纹、源码坐标、严重级别、最长前缀与报告排序均可从输入复算</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="33" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现自由度</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>函数拆分、变量名、注释、内部索引结构、CSV必要引号和LF或CRLF行尾</x:v>
+        <x:v>函数拆分、变量名、注释和内部索引结构可以不同，CSV允许必要引号及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R688b2e2e9fb945fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R34c38072b5fb4b9e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,15 +346,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>脱敏CSP浏览器上报、发布制品索引、简化source map和安全分流策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+        <x:v>本次CSP浏览器上报、发布制品索引、source map和安全分流策略，账号与流量字段已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取data、config、source_maps、rules和starter</x:v>
+        <x:v>整理CSP违规上报，压制已知噪声并反查源码，为安全值班生成可分派的告警汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -373,12 +373,12 @@
         <x:v>output/src/triage_csp_reports.mjs；output/reports/normalized_violations.csv；output/reports/source_lookup.csv；output/reports/suppressed_reports.csv；output/reports/alert_rollup.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>逐行解析；规范化URL；策略压制；生成指纹；去重；反查源码；赋级归属；聚合告警；导出报告</x:v>
+        <x:v>用Node.js逐行解析上报并规范化URL，按策略压制后生成指纹、去重、反查源码、分配严重级别与负责人，再聚合告警并导出报告</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" customHeight="1">
@@ -431,34 +431,34 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>正式处理只读本地脱敏材料，不连接浏览器、SIEM或外部告警系统</x:v>
+        <x:v>只读取随包上报、制品索引、source map和策略，不连接浏览器、SIEM或外部告警系统</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>npm run process返回0，完成版模块和四张CSV可读，跨表report_id、fingerprint、source_path及owner_hint闭合</x:v>
+        <x:v>交付完成版模块和四份CSV，跨表report_id、fingerprint、source_path及owner_hint闭合</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>结果核对</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>物理行去向、压制原因、URL字段、策略指纹、源码坐标、严重级别、最长前缀与报告排序均可从输入复算</x:v>
+        <x:v>核对物理行去向、压制原因、URL字段、策略指纹、源码坐标、严重级别、最长前缀与报告排序</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="33" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>实现自由度</x:v>
+        <x:v>允许变体</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>函数拆分、变量名、注释和内部索引结构可以不同，CSV允许必要引号及LF或CRLF行尾</x:v>
+        <x:v>函数拆分、变量名、注释和内部索引结构可以不同；CSV可使用必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
